--- a/Raw_Data/Valesor 12_updated with OECD values.xlsx
+++ b/Raw_Data/Valesor 12_updated with OECD values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anthesisllc-my.sharepoint.com/personal/lovisa_areback_anthesisgroup_com/Documents/Dokument/GitHub/CBA_GBG_PROT/Raw_Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StefanÅström\C_Verktyg\Python\ALL_PYTHON\2026_v7_Goth_Prot_CBA\Raw_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="174" documentId="8_{6875EADB-AFAD-4E79-A326-5762FBACA071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{233CA821-7F4E-41DA-9796-5270914A310F}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{0EFAC0D5-3333-49E4-993E-3033691A9986}"/>
+    <workbookView xWindow="28680" yWindow="-2850" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{0EFAC0D5-3333-49E4-993E-3033691A9986}"/>
   </bookViews>
   <sheets>
     <sheet name="VALESOR VOLY VSL vQALY" sheetId="50" r:id="rId1"/>
@@ -1174,15 +1174,15 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultColWidth="9.07421875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.4609375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.3046875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.4609375" style="10" customWidth="1"/>
-    <col min="4" max="16384" width="9.07421875" style="1"/>
+    <col min="1" max="1" width="22.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="10" customWidth="1"/>
+    <col min="4" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="5" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" s="5" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D1" s="4"/>
     </row>
-    <row r="2" spans="1:4" s="6" customFormat="1" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" s="6" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>3688168.7816651617</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>191</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>10435709</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>4</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>4570100</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>1796000</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>6</v>
       </c>
@@ -1251,7 +1251,7 @@
         <v>2108600</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>7</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>4085900</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>8</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>2010600</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" s="12" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>9</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>6759200</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>10</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>5622200</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>11</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>5391300</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>12</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>2630000</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>13</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>3035400</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>14</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>4164900</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>15</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>4307600</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>16</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>9905057</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>17</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>3907300</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>18</v>
       </c>
@@ -1383,7 +1383,7 @@
         <v>7753380</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>19</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>4753600</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>20</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>5637800</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>21</v>
       </c>
@@ -1416,7 +1416,7 @@
         <v>2837200</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>22</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>3418500</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>23</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>9395400</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>24</v>
       </c>
@@ -1449,7 +1449,7 @@
         <v>4268900</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>25</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>3145400</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>26</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>3964000</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>27</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>11726700</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>28</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>4802100</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>29</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>6013600</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>30</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>3563100</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>31</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>3455300</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>32</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>3303400</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>33</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>3393900</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>34</v>
       </c>
@@ -1559,7 +1559,7 @@
         <v>4012500</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>35</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>3778200</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>36</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>9043688</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>37</v>
       </c>
@@ -1592,7 +1592,7 @@
         <v>4633400</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>38</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>9500711</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>39</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>16455153</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>40</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>7012800</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>41</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>2755200</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>42</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>1412800</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>43</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>1456800</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>44</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>2389400</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>45</v>
       </c>
@@ -1680,7 +1680,7 @@
         <v>1613100</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>46</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>2789800</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>47</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>497500</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>48</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>1299500</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>49</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>3025300</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>50</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>351000</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>51</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>1449800</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>52</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>1493000</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>53</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>812000</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>54</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>1394100</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>55</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>1572600</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>56</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>2000800</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>57</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>1917700</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>58</v>
       </c>
@@ -1831,9 +1831,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE8B8A2-BF3A-470F-9237-679DFD2B1EC9}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>59</v>
       </c>
@@ -1843,7 +1843,7 @@
       <c r="E1" s="14"/>
       <c r="F1" s="14"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>60</v>
       </c>
@@ -1853,7 +1853,7 @@
       <c r="E2" s="17"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>61</v>
       </c>
@@ -1871,21 +1871,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{982B86D4-CBD8-4B89-A9AA-CC8A373AFD75}">
   <dimension ref="A1:N76"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="15.69140625" customWidth="1"/>
-    <col min="5" max="5" width="16.765625" customWidth="1"/>
-    <col min="6" max="6" width="11.3046875" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.765625" customWidth="1"/>
-    <col min="9" max="9" width="42.765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.77734375" customWidth="1"/>
+    <col min="9" max="9" width="42.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="20.4609375" customWidth="1"/>
-    <col min="12" max="12" width="14.84375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.44140625" customWidth="1"/>
+    <col min="12" max="12" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>126</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2020</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2020</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2020</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>2961500</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2020</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>10093121</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2020</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2020</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2020</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2020</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2020</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>3722716</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2020</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>19482117</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2020</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>6726596</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2020</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2020</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2020</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2020</v>
       </c>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2020</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2020</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2020</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2020</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2020</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>9749310</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2020</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>6949912</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2020</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2020</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>33586372</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2020</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2020</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>83384680</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2020</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>2020</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2020</v>
       </c>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>2020</v>
       </c>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>2020</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>2020</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>2020</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>2020</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>2020</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>2020</v>
       </c>
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>2020</v>
       </c>
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>2020</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>2020</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>2020</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>2020</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>2020</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>2020</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>2020</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>2020</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>2020</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>2020</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>2020</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>2020</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>2020</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>2020</v>
       </c>
@@ -3691,7 +3691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>2020</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>2020</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>2020</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>2020</v>
       </c>
@@ -3827,7 +3827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B58" s="18"/>
       <c r="D58" s="18"/>
       <c r="L58" s="19">
@@ -3839,23 +3839,23 @@
         <v>176656324</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B59" s="18"/>
       <c r="D59" s="18"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>63</v>
       </c>
       <c r="B60" s="18"/>
       <c r="D60" s="18"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="76" spans="8:10" x14ac:dyDescent="0.4">
+    <row r="76" spans="8:10" x14ac:dyDescent="0.3">
       <c r="H76" t="s">
         <v>28</v>
       </c>
@@ -3871,13 +3871,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFA50F39-0B64-4B49-A2C5-537DBA68F68B}">
   <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.765625" customWidth="1"/>
-    <col min="2" max="16" width="50.765625" customWidth="1"/>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="16" width="50.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>169</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>153</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>142</v>
       </c>
@@ -4030,6 +4030,81 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="458478d6-e45f-463e-b166-5a01b5e53481">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="64bc8f4d-cac8-469d-840e-d8b6f8e247f0" xsi:nil="true"/>
+    <_dlc_DocId xmlns="64bc8f4d-cac8-469d-840e-d8b6f8e247f0">4FMPXW5WT43S-1005746519-444</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="64bc8f4d-cac8-469d-840e-d8b6f8e247f0">
+      <Url>https://anthesisllc.sharepoint.com/teams/External_-_Nordic_SLCPs_365/_layouts/15/DocIdRedir.aspx?ID=4FMPXW5WT43S-1005746519-444</Url>
+      <Description>4FMPXW5WT43S-1005746519-444</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="dokument" ma:contentTypeID="0x010100EE726821B4414D4F801789566814E9B0" ma:contentTypeVersion="14" ma:contentTypeDescription="Skapa ett nytt dokument." ma:contentTypeScope="" ma:versionID="9640bda3b9888aac721eb9060946fcb8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="64bc8f4d-cac8-469d-840e-d8b6f8e247f0" xmlns:ns3="458478d6-e45f-463e-b166-5a01b5e53481" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f4623e60d5b6808aeaedb8b4af22e75" ns2:_="" ns3:_="">
     <xsd:import namespace="64bc8f4d-cac8-469d-840e-d8b6f8e247f0"/>
@@ -4283,82 +4358,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="458478d6-e45f-463e-b166-5a01b5e53481">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="64bc8f4d-cac8-469d-840e-d8b6f8e247f0" xsi:nil="true"/>
-    <_dlc_DocId xmlns="64bc8f4d-cac8-469d-840e-d8b6f8e247f0">4FMPXW5WT43S-1005746519-444</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="64bc8f4d-cac8-469d-840e-d8b6f8e247f0">
-      <Url>https://anthesisllc.sharepoint.com/teams/External_-_Nordic_SLCPs_365/_layouts/15/DocIdRedir.aspx?ID=4FMPXW5WT43S-1005746519-444</Url>
-      <Description>4FMPXW5WT43S-1005746519-444</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{345157FC-9AB7-471E-8A38-484235567C74}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A959997-138A-426D-9C5C-866D09D94D10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA28B098-AA57-4494-8DA3-761B84790965}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="458478d6-e45f-463e-b166-5a01b5e53481"/>
+    <ds:schemaRef ds:uri="64bc8f4d-cac8-469d-840e-d8b6f8e247f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C45305E3-4428-404D-9053-86A1EAC91634}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4375,31 +4402,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA28B098-AA57-4494-8DA3-761B84790965}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="458478d6-e45f-463e-b166-5a01b5e53481"/>
-    <ds:schemaRef ds:uri="64bc8f4d-cac8-469d-840e-d8b6f8e247f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A959997-138A-426D-9C5C-866D09D94D10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{345157FC-9AB7-471E-8A38-484235567C74}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>